--- a/BusinessCase1/BankClients_Metadata.xlsx
+++ b/BusinessCase1/BankClients_Metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leon\Desktop\FINTECH\BusinessCase1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leon\Desktop\FINTECH\Fintech\BusinessCase1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1685BB-D6FD-46D6-A42A-E800AEEA2AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313A3189-9D62-40F2-99C4-B2401CB7610B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="315" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -140,6 +140,18 @@
   </si>
   <si>
     <t>Investment type: 1 = no investments; 2 = mostly lump sum; 3 = mostly capital accumulation (gradual investment with monthly payments)</t>
+  </si>
+  <si>
+    <t>ordinal</t>
+  </si>
+  <si>
+    <t>nominal</t>
+  </si>
+  <si>
+    <t>Nominal</t>
+  </si>
+  <si>
+    <t>Numerical</t>
   </si>
 </sst>
 </file>
@@ -163,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +185,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -189,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -198,6 +216,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,20 +503,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="2"/>
+    <col min="3" max="3" width="10.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -500,79 +525,94 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C3" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -580,7 +620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -588,7 +628,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -596,7 +636,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -604,7 +644,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -613,7 +653,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
